--- a/Employee_Reports_wi48/Jeffrey Sayson Bagatua Q0536.xlsx
+++ b/Employee_Reports_wi48/Jeffrey Sayson Bagatua Q0536.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
